--- a/main/StructureDefinition-Patient.xlsx
+++ b/main/StructureDefinition-Patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-12</t>
+    <t>2026-02-05</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright 2020-2025 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
+    <t>Copyright 2020-2026 Unabhängige Treuhandstelle der Universitätsmedizin Greifswald</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/main/StructureDefinition-Patient.xlsx
+++ b/main/StructureDefinition-Patient.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6437" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6437" uniqueCount="860">
   <si>
     <t>Property</t>
   </si>
@@ -646,16 +646,16 @@
     <t>The registered place of birth of the patient. A sytem may use the address.text if they don't store the birthPlace address in discrete elements.</t>
   </si>
   <si>
-    <t>Patient.extension:birthPlace.id</t>
-  </si>
-  <si>
-    <t>Patient.extension.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Patient.extension:birthPlace.id</t>
+  </si>
+  <si>
+    <t>Patient.extension.id</t>
+  </si>
+  <si>
     <t>Patient.extension:birthPlace.extension</t>
   </si>
   <si>
@@ -696,14 +696,10 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ext-1
-</t>
   </si>
   <si>
     <t>Patient.extension:birthPlace.value[x].id</t>
@@ -1033,9 +1029,6 @@
     <t>Patient.extension:nationality.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
     <t>Patient.extension:nationality.extension:code</t>
   </si>
   <si>
@@ -1315,7 +1308,7 @@
   </si>
   <si>
     <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
     <t>Patient.extension:customIdatValues</t>
@@ -5138,7 +5131,7 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>117</v>
@@ -5161,10 +5154,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5187,7 +5180,7 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>103</v>
@@ -5253,7 +5246,7 @@
         <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>20</v>
@@ -5600,7 +5593,7 @@
         <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>100</v>
@@ -5623,10 +5616,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5738,10 +5731,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5855,10 +5848,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5884,16 +5877,16 @@
         <v>164</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5906,43 +5899,43 @@
         <v>20</v>
       </c>
       <c r="T25" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X25" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="U25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X25" t="s" s="2">
+      <c r="Y25" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="Z25" t="s" s="2">
+      <c r="AA25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5957,16 +5950,16 @@
         <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -5974,10 +5967,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6003,13 +5996,13 @@
         <v>164</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -6023,43 +6016,43 @@
         <v>20</v>
       </c>
       <c r="T26" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y26" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="U26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X26" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="Y26" t="s" s="2">
+      <c r="Z26" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AA26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -6074,7 +6067,7 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
@@ -6083,7 +6076,7 @@
         <v>20</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -6091,10 +6084,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6120,16 +6113,16 @@
         <v>102</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -6142,43 +6135,43 @@
         <v>20</v>
       </c>
       <c r="T27" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -6193,16 +6186,16 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -6210,10 +6203,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>254</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6239,10 +6232,10 @@
         <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6257,43 +6250,43 @@
         <v>20</v>
       </c>
       <c r="T28" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -6308,16 +6301,16 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>20</v>
@@ -6325,14 +6318,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -6354,10 +6347,10 @@
         <v>102</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -6372,43 +6365,43 @@
         <v>20</v>
       </c>
       <c r="T29" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -6423,16 +6416,16 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -6440,14 +6433,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -6469,13 +6462,13 @@
         <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6489,43 +6482,43 @@
         <v>20</v>
       </c>
       <c r="T30" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -6540,16 +6533,16 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -6557,14 +6550,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6586,10 +6579,10 @@
         <v>102</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6640,7 +6633,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6655,16 +6648,16 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -6672,14 +6665,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6701,10 +6694,10 @@
         <v>102</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6719,43 +6712,43 @@
         <v>20</v>
       </c>
       <c r="T32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6770,16 +6763,16 @@
         <v>100</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6787,10 +6780,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6816,13 +6809,13 @@
         <v>102</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6872,7 +6865,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6887,16 +6880,16 @@
         <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -6904,10 +6897,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6930,17 +6923,17 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6953,43 +6946,43 @@
         <v>20</v>
       </c>
       <c r="T34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -7004,16 +6997,16 @@
         <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -7021,13 +7014,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>188</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>20</v>
@@ -7049,13 +7042,13 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7115,7 +7108,7 @@
         <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>117</v>
@@ -7138,10 +7131,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7164,7 +7157,7 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>103</v>
@@ -7230,7 +7223,7 @@
         <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>20</v>
@@ -7253,7 +7246,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>201</v>
@@ -7285,7 +7278,7 @@
         <v>110</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>111</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>112</v>
@@ -7370,13 +7363,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>201</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>20</v>
@@ -7487,10 +7480,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7513,7 +7506,7 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>103</v>
@@ -7579,7 +7572,7 @@
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>20</v>
@@ -7602,10 +7595,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7717,10 +7710,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7760,7 +7753,7 @@
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>20</v>
@@ -7834,10 +7827,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7860,7 +7853,7 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>212</v>
@@ -7893,11 +7886,11 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -7924,7 +7917,7 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>100</v>
@@ -7947,10 +7940,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8062,10 +8055,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8179,10 +8172,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8208,16 +8201,16 @@
         <v>142</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -8266,7 +8259,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -8281,7 +8274,7 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>20</v>
@@ -8290,7 +8283,7 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -8298,10 +8291,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8413,10 +8406,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8530,10 +8523,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8559,16 +8552,16 @@
         <v>130</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -8617,7 +8610,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8632,7 +8625,7 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>20</v>
@@ -8641,7 +8634,7 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -8649,10 +8642,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8678,13 +8671,13 @@
         <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8734,7 +8727,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8749,7 +8742,7 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>20</v>
@@ -8758,7 +8751,7 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -8766,10 +8759,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8795,14 +8788,14 @@
         <v>164</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -8851,7 +8844,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8866,7 +8859,7 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>20</v>
@@ -8875,7 +8868,7 @@
         <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -8883,10 +8876,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8912,14 +8905,14 @@
         <v>102</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8968,7 +8961,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8983,7 +8976,7 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>20</v>
@@ -8992,7 +8985,7 @@
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -9000,10 +8993,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9026,19 +9019,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -9087,7 +9080,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -9102,7 +9095,7 @@
         <v>100</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>20</v>
@@ -9111,7 +9104,7 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -9119,10 +9112,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9148,16 +9141,16 @@
         <v>102</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -9206,7 +9199,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -9221,7 +9214,7 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>20</v>
@@ -9230,7 +9223,7 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -9238,13 +9231,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>201</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>20</v>
@@ -9269,10 +9262,10 @@
         <v>109</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9355,10 +9348,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9381,7 +9374,7 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>103</v>
@@ -9447,7 +9440,7 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>20</v>
@@ -9470,10 +9463,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9585,10 +9578,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9628,7 +9621,7 @@
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>20</v>
@@ -9702,10 +9695,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9728,7 +9721,7 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>212</v>
@@ -9794,7 +9787,7 @@
         <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>100</v>
@@ -9817,7 +9810,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>203</v>
@@ -9860,7 +9853,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>20</v>
@@ -9934,7 +9927,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>210</v>
@@ -9960,7 +9953,7 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>212</v>
@@ -10026,7 +10019,7 @@
         <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>100</v>
@@ -10049,19 +10042,19 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>188</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>78</v>
@@ -10079,13 +10072,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10145,7 +10138,7 @@
         <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>117</v>
@@ -10168,10 +10161,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10197,16 +10190,16 @@
         <v>109</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -10255,7 +10248,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -10287,10 +10280,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10313,17 +10306,17 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -10372,7 +10365,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -10387,16 +10380,16 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -10404,10 +10397,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10519,10 +10512,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10636,10 +10629,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10665,16 +10658,16 @@
         <v>164</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10699,31 +10692,31 @@
         <v>20</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10738,7 +10731,7 @@
         <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>20</v>
@@ -10755,10 +10748,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10781,19 +10774,19 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10821,28 +10814,28 @@
         <v>146</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10857,7 +10850,7 @@
         <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>20</v>
@@ -10866,7 +10859,7 @@
         <v>20</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10874,10 +10867,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10903,16 +10896,16 @@
         <v>130</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10925,7 +10918,7 @@
         <v>20</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>20</v>
@@ -10961,7 +10954,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10976,7 +10969,7 @@
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>20</v>
@@ -10985,7 +10978,7 @@
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10993,10 +10986,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11022,13 +11015,13 @@
         <v>102</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11042,7 +11035,7 @@
         <v>20</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>20</v>
@@ -11078,7 +11071,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -11093,7 +11086,7 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>20</v>
@@ -11102,7 +11095,7 @@
         <v>20</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -11110,10 +11103,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11136,13 +11129,13 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11193,7 +11186,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -11208,7 +11201,7 @@
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>20</v>
@@ -11217,7 +11210,7 @@
         <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -11225,10 +11218,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11251,16 +11244,16 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11310,7 +11303,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -11325,7 +11318,7 @@
         <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>20</v>
@@ -11334,7 +11327,7 @@
         <v>20</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -11342,10 +11335,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11368,26 +11361,26 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N72" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="P72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q72" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="O72" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q72" t="s" s="2">
-        <v>491</v>
-      </c>
       <c r="R72" t="s" s="2">
         <v>20</v>
       </c>
@@ -11431,7 +11424,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -11446,13 +11439,13 @@
         <v>100</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>20</v>
@@ -11463,10 +11456,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11489,19 +11482,19 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -11550,7 +11543,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11565,16 +11558,16 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -11582,10 +11575,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11697,10 +11690,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11814,10 +11807,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11843,16 +11836,16 @@
         <v>164</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -11877,31 +11870,31 @@
         <v>20</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11916,7 +11909,7 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>20</v>
@@ -11925,7 +11918,7 @@
         <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -11933,10 +11926,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11962,16 +11955,16 @@
         <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M77" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="O77" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>20</v>
@@ -12020,7 +12013,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -12035,7 +12028,7 @@
         <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>20</v>
@@ -12044,7 +12037,7 @@
         <v>20</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
@@ -12052,14 +12045,14 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -12081,13 +12074,13 @@
         <v>102</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N78" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -12137,7 +12130,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -12152,7 +12145,7 @@
         <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>20</v>
@@ -12161,7 +12154,7 @@
         <v>20</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -12169,14 +12162,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -12198,13 +12191,13 @@
         <v>102</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N79" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12254,7 +12247,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -12269,7 +12262,7 @@
         <v>100</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>20</v>
@@ -12278,7 +12271,7 @@
         <v>20</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -12286,10 +12279,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12315,10 +12308,10 @@
         <v>102</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12369,7 +12362,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12384,7 +12377,7 @@
         <v>100</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>20</v>
@@ -12393,7 +12386,7 @@
         <v>20</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -12401,10 +12394,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12430,10 +12423,10 @@
         <v>102</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12516,10 +12509,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12629,13 +12622,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B83" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="C83" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="D83" t="s" s="2">
         <v>20</v>
@@ -12657,16 +12650,16 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12725,13 +12718,13 @@
         <v>79</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>117</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>20</v>
@@ -12748,10 +12741,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12774,7 +12767,7 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="L84" t="s" s="2">
         <v>103</v>
@@ -12840,7 +12833,7 @@
         <v>88</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>199</v>
+        <v>20</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>20</v>
@@ -12863,10 +12856,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12978,10 +12971,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13021,7 +13014,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>20</v>
@@ -13095,10 +13088,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13136,7 +13129,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>20</v>
@@ -13154,11 +13147,11 @@
         <v>20</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>20</v>
@@ -13185,7 +13178,7 @@
         <v>88</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>215</v>
+        <v>20</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>100</v>
@@ -13208,10 +13201,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13237,10 +13230,10 @@
         <v>102</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -13264,7 +13257,7 @@
         <v>20</v>
       </c>
       <c r="W88" t="s" s="2">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="X88" t="s" s="2">
         <v>20</v>
@@ -13291,7 +13284,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -13323,10 +13316,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13352,10 +13345,10 @@
         <v>102</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13406,7 +13399,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13421,7 +13414,7 @@
         <v>100</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>20</v>
@@ -13430,7 +13423,7 @@
         <v>20</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -13438,10 +13431,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13464,17 +13457,17 @@
         <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -13523,7 +13516,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13538,7 +13531,7 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>20</v>
@@ -13547,7 +13540,7 @@
         <v>20</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13555,10 +13548,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13581,19 +13574,19 @@
         <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="O91" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -13630,7 +13623,7 @@
         <v>20</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AC91" s="2"/>
       <c r="AD91" t="s" s="2">
@@ -13640,7 +13633,7 @@
         <v>115</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13655,16 +13648,16 @@
         <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AL91" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
@@ -13672,13 +13665,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>20</v>
@@ -13700,19 +13693,19 @@
         <v>89</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="L92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13761,7 +13754,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13776,16 +13769,16 @@
         <v>100</v>
       </c>
       <c r="AK92" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13793,10 +13786,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13908,10 +13901,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14025,10 +14018,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14054,10 +14047,10 @@
         <v>164</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14069,7 +14062,7 @@
         <v>20</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>20</v>
@@ -14084,46 +14077,46 @@
         <v>20</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="Z95" t="s" s="2">
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI95" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>20</v>
@@ -14132,7 +14125,7 @@
         <v>20</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>20</v>
@@ -14140,10 +14133,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14169,16 +14162,16 @@
         <v>102</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -14227,7 +14220,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14242,7 +14235,7 @@
         <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>20</v>
@@ -14251,7 +14244,7 @@
         <v>20</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>20</v>
@@ -14259,10 +14252,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14288,16 +14281,16 @@
         <v>164</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>20</v>
@@ -14322,31 +14315,31 @@
         <v>20</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y97" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF97" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -14361,7 +14354,7 @@
         <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>20</v>
@@ -14370,7 +14363,7 @@
         <v>20</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>20</v>
@@ -14378,10 +14371,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14404,16 +14397,16 @@
         <v>89</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M98" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="N98" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14463,7 +14456,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14495,10 +14488,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14521,13 +14514,13 @@
         <v>89</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14578,7 +14571,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14593,7 +14586,7 @@
         <v>100</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>20</v>
@@ -14610,13 +14603,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>20</v>
@@ -14638,19 +14631,19 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>20</v>
@@ -14699,7 +14692,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14714,16 +14707,16 @@
         <v>100</v>
       </c>
       <c r="AK100" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>20</v>
@@ -14731,10 +14724,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14846,10 +14839,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14963,10 +14956,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14992,10 +14985,10 @@
         <v>164</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15007,7 +15000,7 @@
         <v>20</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>20</v>
@@ -15022,46 +15015,46 @@
         <v>20</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y103" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="Z103" t="s" s="2">
+      <c r="AG103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI103" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>20</v>
@@ -15070,7 +15063,7 @@
         <v>20</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>20</v>
@@ -15078,10 +15071,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15107,16 +15100,16 @@
         <v>102</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="N104" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>20</v>
@@ -15165,7 +15158,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -15180,7 +15173,7 @@
         <v>100</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>20</v>
@@ -15189,7 +15182,7 @@
         <v>20</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>20</v>
@@ -15197,10 +15190,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15226,16 +15219,16 @@
         <v>164</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>20</v>
@@ -15260,31 +15253,31 @@
         <v>20</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y105" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF105" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15299,7 +15292,7 @@
         <v>100</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>20</v>
@@ -15308,7 +15301,7 @@
         <v>20</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>20</v>
@@ -15316,10 +15309,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15342,16 +15335,16 @@
         <v>89</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>629</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -15401,7 +15394,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15433,10 +15426,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15459,13 +15452,13 @@
         <v>89</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15516,7 +15509,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15531,7 +15524,7 @@
         <v>100</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>20</v>
@@ -15548,10 +15541,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15577,16 +15570,16 @@
         <v>164</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="N108" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="M108" t="s" s="2">
+      <c r="O108" t="s" s="2">
         <v>650</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>652</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>20</v>
@@ -15611,13 +15604,13 @@
         <v>20</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>20</v>
@@ -15635,7 +15628,7 @@
         <v>20</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15650,16 +15643,16 @@
         <v>100</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN108" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>657</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>20</v>
@@ -15667,10 +15660,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15693,19 +15686,19 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>661</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>20</v>
@@ -15754,7 +15747,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15769,27 +15762,27 @@
         <v>100</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="AL109" t="s" s="2">
+      <c r="AO109" t="s" s="2">
         <v>665</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>667</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15812,19 +15805,19 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="N110" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="M110" t="s" s="2">
+      <c r="O110" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>20</v>
@@ -15873,7 +15866,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15888,7 +15881,7 @@
         <v>100</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>106</v>
@@ -15897,7 +15890,7 @@
         <v>20</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>20</v>
@@ -15905,10 +15898,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15934,16 +15927,16 @@
         <v>211</v>
       </c>
       <c r="L111" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="N111" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="M111" t="s" s="2">
+      <c r="O111" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>680</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>20</v>
@@ -15992,7 +15985,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -16007,16 +16000,16 @@
         <v>100</v>
       </c>
       <c r="AK111" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN111" t="s" s="2">
         <v>681</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>20</v>
@@ -16024,10 +16017,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16139,10 +16132,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16256,10 +16249,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16285,16 +16278,16 @@
         <v>164</v>
       </c>
       <c r="L114" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="N114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>20</v>
@@ -16307,43 +16300,43 @@
         <v>20</v>
       </c>
       <c r="T114" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X114" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="U114" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X114" t="s" s="2">
+      <c r="Y114" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="Y114" t="s" s="2">
+      <c r="Z114" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="Z114" t="s" s="2">
+      <c r="AA114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF114" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16358,16 +16351,16 @@
         <v>100</v>
       </c>
       <c r="AK114" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN114" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>20</v>
@@ -16375,10 +16368,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16404,13 +16397,13 @@
         <v>164</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M115" t="s" s="2">
+      <c r="N115" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -16424,43 +16417,43 @@
         <v>20</v>
       </c>
       <c r="T115" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="Y115" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="U115" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="Y115" t="s" s="2">
+      <c r="Z115" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="Z115" t="s" s="2">
+      <c r="AA115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF115" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16475,7 +16468,7 @@
         <v>100</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>20</v>
@@ -16484,7 +16477,7 @@
         <v>20</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>20</v>
@@ -16492,10 +16485,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16521,16 +16514,16 @@
         <v>102</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M116" t="s" s="2">
+      <c r="N116" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N116" t="s" s="2">
+      <c r="O116" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>20</v>
@@ -16543,43 +16536,43 @@
         <v>20</v>
       </c>
       <c r="T116" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF116" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16594,16 +16587,16 @@
         <v>100</v>
       </c>
       <c r="AK116" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN116" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>20</v>
@@ -16611,10 +16604,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16640,10 +16633,10 @@
         <v>102</v>
       </c>
       <c r="L117" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M117" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -16658,43 +16651,43 @@
         <v>20</v>
       </c>
       <c r="T117" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF117" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16709,16 +16702,16 @@
         <v>100</v>
       </c>
       <c r="AK117" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN117" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>20</v>
@@ -16726,14 +16719,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16755,10 +16748,10 @@
         <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M118" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16773,43 +16766,43 @@
         <v>20</v>
       </c>
       <c r="T118" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF118" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16824,16 +16817,16 @@
         <v>100</v>
       </c>
       <c r="AK118" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN118" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>20</v>
@@ -16841,14 +16834,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -16870,13 +16863,13 @@
         <v>102</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M119" t="s" s="2">
+      <c r="N119" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -16890,43 +16883,43 @@
         <v>20</v>
       </c>
       <c r="T119" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF119" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16941,16 +16934,16 @@
         <v>100</v>
       </c>
       <c r="AK119" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN119" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>20</v>
@@ -16958,14 +16951,14 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
@@ -16987,10 +16980,10 @@
         <v>102</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17017,11 +17010,11 @@
         <v>20</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>20</v>
@@ -17039,7 +17032,7 @@
         <v>20</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -17054,16 +17047,16 @@
         <v>100</v>
       </c>
       <c r="AK120" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN120" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>20</v>
@@ -17071,14 +17064,14 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
@@ -17100,10 +17093,10 @@
         <v>102</v>
       </c>
       <c r="L121" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M121" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -17118,43 +17111,43 @@
         <v>20</v>
       </c>
       <c r="T121" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF121" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -17169,16 +17162,16 @@
         <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN121" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>20</v>
@@ -17186,10 +17179,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17215,13 +17208,13 @@
         <v>102</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17247,11 +17240,11 @@
         <v>20</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>20</v>
@@ -17269,7 +17262,7 @@
         <v>20</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -17284,16 +17277,16 @@
         <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN122" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>20</v>
@@ -17301,10 +17294,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17327,17 +17320,17 @@
         <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L123" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>20</v>
@@ -17350,43 +17343,43 @@
         <v>20</v>
       </c>
       <c r="T123" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF123" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17401,16 +17394,16 @@
         <v>100</v>
       </c>
       <c r="AK123" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN123" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>20</v>
@@ -17418,10 +17411,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17444,17 +17437,17 @@
         <v>20</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>20</v>
@@ -17482,10 +17475,10 @@
         <v>168</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>20</v>
@@ -17503,7 +17496,7 @@
         <v>20</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17518,16 +17511,16 @@
         <v>100</v>
       </c>
       <c r="AK124" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN124" t="s" s="2">
         <v>707</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="AO124" t="s" s="2">
         <v>20</v>
@@ -17535,10 +17528,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17650,10 +17643,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17767,10 +17760,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17796,16 +17789,16 @@
         <v>142</v>
       </c>
       <c r="L127" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M127" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N127" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M127" t="s" s="2">
+      <c r="O127" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>20</v>
@@ -17854,7 +17847,7 @@
         <v>20</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -17869,7 +17862,7 @@
         <v>100</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AL127" t="s" s="2">
         <v>20</v>
@@ -17878,7 +17871,7 @@
         <v>20</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>20</v>
@@ -17886,10 +17879,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18001,10 +17994,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18118,10 +18111,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18147,16 +18140,16 @@
         <v>130</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N130" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="O130" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>20</v>
@@ -18205,7 +18198,7 @@
         <v>20</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>78</v>
@@ -18220,7 +18213,7 @@
         <v>100</v>
       </c>
       <c r="AK130" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AL130" t="s" s="2">
         <v>20</v>
@@ -18229,7 +18222,7 @@
         <v>20</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>20</v>
@@ -18237,10 +18230,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18266,13 +18259,13 @@
         <v>102</v>
       </c>
       <c r="L131" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -18322,7 +18315,7 @@
         <v>20</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -18337,7 +18330,7 @@
         <v>100</v>
       </c>
       <c r="AK131" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AL131" t="s" s="2">
         <v>20</v>
@@ -18346,7 +18339,7 @@
         <v>20</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>20</v>
@@ -18354,10 +18347,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18383,14 +18376,14 @@
         <v>164</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>20</v>
@@ -18439,7 +18432,7 @@
         <v>20</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>78</v>
@@ -18454,7 +18447,7 @@
         <v>100</v>
       </c>
       <c r="AK132" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AL132" t="s" s="2">
         <v>20</v>
@@ -18463,7 +18456,7 @@
         <v>20</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>20</v>
@@ -18471,10 +18464,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18500,14 +18493,14 @@
         <v>102</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>20</v>
@@ -18556,7 +18549,7 @@
         <v>20</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>78</v>
@@ -18571,7 +18564,7 @@
         <v>100</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AL133" t="s" s="2">
         <v>20</v>
@@ -18580,7 +18573,7 @@
         <v>20</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>20</v>
@@ -18588,10 +18581,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18614,19 +18607,19 @@
         <v>89</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M134" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="N134" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M134" t="s" s="2">
+      <c r="O134" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>20</v>
@@ -18675,7 +18668,7 @@
         <v>20</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>78</v>
@@ -18690,7 +18683,7 @@
         <v>100</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AL134" t="s" s="2">
         <v>20</v>
@@ -18699,7 +18692,7 @@
         <v>20</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>20</v>
@@ -18707,10 +18700,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18736,16 +18729,16 @@
         <v>102</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N135" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M135" t="s" s="2">
+      <c r="O135" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>20</v>
@@ -18794,7 +18787,7 @@
         <v>20</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18809,7 +18802,7 @@
         <v>100</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>20</v>
@@ -18818,7 +18811,7 @@
         <v>20</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>20</v>
@@ -18826,10 +18819,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18852,19 +18845,19 @@
         <v>20</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>722</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="O136" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>726</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>20</v>
@@ -18913,7 +18906,7 @@
         <v>20</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>78</v>
@@ -18928,7 +18921,7 @@
         <v>100</v>
       </c>
       <c r="AK136" t="s" s="2">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="AL136" t="s" s="2">
         <v>106</v>
@@ -18937,7 +18930,7 @@
         <v>20</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>20</v>
@@ -18945,10 +18938,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18971,19 +18964,19 @@
         <v>20</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>728</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>731</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="O137" t="s" s="2">
         <v>732</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>734</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>20</v>
@@ -19032,7 +19025,7 @@
         <v>20</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>78</v>
@@ -19047,7 +19040,7 @@
         <v>100</v>
       </c>
       <c r="AK137" t="s" s="2">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="AL137" t="s" s="2">
         <v>106</v>
@@ -19056,7 +19049,7 @@
         <v>20</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>20</v>
@@ -19064,10 +19057,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19090,19 +19083,19 @@
         <v>20</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="M138" t="s" s="2">
         <v>738</v>
       </c>
-      <c r="L138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>739</v>
       </c>
-      <c r="M138" t="s" s="2">
+      <c r="O138" t="s" s="2">
         <v>740</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>742</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>20</v>
@@ -19151,7 +19144,7 @@
         <v>20</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -19163,10 +19156,10 @@
         <v>20</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="AK138" t="s" s="2">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="AL138" t="s" s="2">
         <v>106</v>
@@ -19183,10 +19176,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19298,10 +19291,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19415,14 +19408,14 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -19444,16 +19437,16 @@
         <v>109</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="N141" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>20</v>
@@ -19502,7 +19495,7 @@
         <v>20</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -19534,10 +19527,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19560,17 +19553,17 @@
         <v>20</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>20</v>
@@ -19598,10 +19591,10 @@
         <v>146</v>
       </c>
       <c r="Y142" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="Z142" t="s" s="2">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>20</v>
@@ -19619,7 +19612,7 @@
         <v>20</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -19634,7 +19627,7 @@
         <v>100</v>
       </c>
       <c r="AK142" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AL142" t="s" s="2">
         <v>106</v>
@@ -19643,7 +19636,7 @@
         <v>20</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>20</v>
@@ -19651,10 +19644,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19677,17 +19670,17 @@
         <v>20</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>20</v>
@@ -19736,7 +19729,7 @@
         <v>20</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -19751,7 +19744,7 @@
         <v>100</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="AL143" t="s" s="2">
         <v>106</v>
@@ -19760,7 +19753,7 @@
         <v>20</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>20</v>
@@ -19768,10 +19761,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19794,19 +19787,19 @@
         <v>20</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="L144" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="N144" t="s" s="2">
         <v>765</v>
       </c>
-      <c r="M144" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>767</v>
-      </c>
       <c r="O144" t="s" s="2">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>20</v>
@@ -19855,7 +19848,7 @@
         <v>20</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>78</v>
@@ -19870,7 +19863,7 @@
         <v>100</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AL144" t="s" s="2">
         <v>106</v>
@@ -19879,7 +19872,7 @@
         <v>20</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>20</v>
@@ -19887,10 +19880,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19916,14 +19909,14 @@
         <v>211</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>20</v>
@@ -19972,7 +19965,7 @@
         <v>20</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>78</v>
@@ -19987,7 +19980,7 @@
         <v>100</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>106</v>
@@ -19996,7 +19989,7 @@
         <v>20</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>20</v>
@@ -20004,10 +19997,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20033,14 +20026,14 @@
         <v>164</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>20</v>
@@ -20065,13 +20058,13 @@
         <v>20</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>20</v>
@@ -20089,7 +20082,7 @@
         <v>20</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>78</v>
@@ -20104,7 +20097,7 @@
         <v>100</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="AL146" t="s" s="2">
         <v>106</v>
@@ -20113,7 +20106,7 @@
         <v>20</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>20</v>
@@ -20121,10 +20114,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20147,17 +20140,17 @@
         <v>20</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>20</v>
@@ -20206,7 +20199,7 @@
         <v>20</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>78</v>
@@ -20215,13 +20208,13 @@
         <v>88</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>106</v>
@@ -20230,7 +20223,7 @@
         <v>20</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>20</v>
@@ -20238,10 +20231,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20264,13 +20257,13 @@
         <v>20</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20321,7 +20314,7 @@
         <v>20</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>78</v>
@@ -20336,7 +20329,7 @@
         <v>100</v>
       </c>
       <c r="AK148" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="AL148" t="s" s="2">
         <v>106</v>
@@ -20353,10 +20346,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20379,19 +20372,19 @@
         <v>20</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>790</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>791</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>793</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>20</v>
@@ -20440,7 +20433,7 @@
         <v>20</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>78</v>
@@ -20455,10 +20448,10 @@
         <v>100</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="AM149" t="s" s="2">
         <v>20</v>
@@ -20472,10 +20465,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20587,10 +20580,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20704,14 +20697,14 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -20733,16 +20726,16 @@
         <v>109</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="N152" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>20</v>
@@ -20791,7 +20784,7 @@
         <v>20</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>78</v>
@@ -20823,10 +20816,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20849,19 +20842,19 @@
         <v>20</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>798</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="N153" t="s" s="2">
         <v>800</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>801</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>803</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>20</v>
@@ -20886,13 +20879,13 @@
         <v>20</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y153" t="s" s="2">
         <v>169</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>20</v>
@@ -20910,7 +20903,7 @@
         <v>20</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>88</v>
@@ -20925,16 +20918,16 @@
         <v>100</v>
       </c>
       <c r="AK153" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN153" t="s" s="2">
         <v>805</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>807</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>20</v>
@@ -20942,10 +20935,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21057,10 +21050,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21174,10 +21167,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21203,16 +21196,16 @@
         <v>142</v>
       </c>
       <c r="L156" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N156" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="M156" t="s" s="2">
+      <c r="O156" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>20</v>
@@ -21261,7 +21254,7 @@
         <v>20</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>78</v>
@@ -21276,7 +21269,7 @@
         <v>100</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="AL156" t="s" s="2">
         <v>20</v>
@@ -21285,7 +21278,7 @@
         <v>20</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>20</v>
@@ -21293,10 +21286,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21408,10 +21401,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21525,10 +21518,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21554,16 +21547,16 @@
         <v>130</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N159" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="O159" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>20</v>
@@ -21612,7 +21605,7 @@
         <v>20</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>78</v>
@@ -21627,7 +21620,7 @@
         <v>100</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>20</v>
@@ -21636,7 +21629,7 @@
         <v>20</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>20</v>
@@ -21644,10 +21637,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21673,13 +21666,13 @@
         <v>102</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N160" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="M160" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -21729,7 +21722,7 @@
         <v>20</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>78</v>
@@ -21744,7 +21737,7 @@
         <v>100</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>20</v>
@@ -21753,7 +21746,7 @@
         <v>20</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>20</v>
@@ -21761,10 +21754,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21790,14 +21783,14 @@
         <v>164</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>20</v>
@@ -21846,7 +21839,7 @@
         <v>20</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>78</v>
@@ -21861,7 +21854,7 @@
         <v>100</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>20</v>
@@ -21870,7 +21863,7 @@
         <v>20</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>20</v>
@@ -21878,10 +21871,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21907,14 +21900,14 @@
         <v>102</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>20</v>
@@ -21963,7 +21956,7 @@
         <v>20</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>78</v>
@@ -21978,7 +21971,7 @@
         <v>100</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>20</v>
@@ -21987,7 +21980,7 @@
         <v>20</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>20</v>
@@ -21995,10 +21988,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22021,19 +22014,19 @@
         <v>89</v>
       </c>
       <c r="K163" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L163" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M163" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L163" t="s" s="2">
+      <c r="N163" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="O163" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>20</v>
@@ -22082,7 +22075,7 @@
         <v>20</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>78</v>
@@ -22097,7 +22090,7 @@
         <v>100</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>20</v>
@@ -22106,7 +22099,7 @@
         <v>20</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>20</v>
@@ -22114,10 +22107,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22143,16 +22136,16 @@
         <v>102</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M164" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N164" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="O164" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N164" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>20</v>
@@ -22201,7 +22194,7 @@
         <v>20</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>78</v>
@@ -22216,7 +22209,7 @@
         <v>100</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>20</v>
@@ -22225,7 +22218,7 @@
         <v>20</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>20</v>
@@ -22233,10 +22226,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22259,26 +22252,26 @@
         <v>20</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="M165" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="N165" t="s" s="2">
         <v>820</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="O165" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>823</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>20</v>
@@ -22320,7 +22313,7 @@
         <v>20</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>78</v>
@@ -22335,16 +22328,16 @@
         <v>100</v>
       </c>
       <c r="AK165" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="AL165" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="AM165" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN165" t="s" s="2">
         <v>825</v>
-      </c>
-      <c r="AL165" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="AM165" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN165" t="s" s="2">
-        <v>827</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>20</v>
@@ -22352,14 +22345,14 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
@@ -22378,16 +22371,16 @@
         <v>20</v>
       </c>
       <c r="K166" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="M166" t="s" s="2">
         <v>830</v>
       </c>
-      <c r="L166" t="s" s="2">
+      <c r="N166" t="s" s="2">
         <v>831</v>
-      </c>
-      <c r="M166" t="s" s="2">
-        <v>832</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>833</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -22437,7 +22430,7 @@
         <v>20</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>78</v>
@@ -22452,7 +22445,7 @@
         <v>100</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="AL166" t="s" s="2">
         <v>106</v>
@@ -22461,7 +22454,7 @@
         <v>20</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>20</v>
@@ -22469,10 +22462,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22495,19 +22488,19 @@
         <v>89</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L167" t="s" s="2">
+        <v>835</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>838</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>839</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>840</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>20</v>
@@ -22556,7 +22549,7 @@
         <v>20</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>78</v>
@@ -22571,10 +22564,10 @@
         <v>100</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>20</v>
@@ -22588,10 +22581,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22614,19 +22607,19 @@
         <v>89</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="L168" t="s" s="2">
+        <v>841</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>843</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="O168" t="s" s="2">
         <v>844</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>845</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>846</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>20</v>
@@ -22675,7 +22668,7 @@
         <v>20</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>78</v>
@@ -22690,7 +22683,7 @@
         <v>100</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="AL168" t="s" s="2">
         <v>106</v>
@@ -22707,10 +22700,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22822,10 +22815,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22939,14 +22932,14 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
@@ -22968,16 +22961,16 @@
         <v>109</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="N171" t="s" s="2">
         <v>112</v>
       </c>
       <c r="O171" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>20</v>
@@ -23026,7 +23019,7 @@
         <v>20</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>78</v>
@@ -23058,10 +23051,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23084,16 +23077,16 @@
         <v>89</v>
       </c>
       <c r="K172" t="s" s="2">
+        <v>850</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="M172" t="s" s="2">
         <v>852</v>
       </c>
-      <c r="L172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>853</v>
-      </c>
-      <c r="M172" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>855</v>
       </c>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
@@ -23143,7 +23136,7 @@
         <v>20</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>88</v>
@@ -23158,7 +23151,7 @@
         <v>100</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>106</v>
@@ -23167,7 +23160,7 @@
         <v>20</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>20</v>
@@ -23175,10 +23168,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23204,10 +23197,10 @@
         <v>164</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -23234,13 +23227,13 @@
         <v>20</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>20</v>
@@ -23258,7 +23251,7 @@
         <v>20</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>88</v>
@@ -23273,7 +23266,7 @@
         <v>100</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>106</v>

--- a/main/StructureDefinition-Patient.xlsx
+++ b/main/StructureDefinition-Patient.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2025.2.0</t>
+    <t>2026.1.0</t>
   </si>
   <si>
     <t>Name</t>
